--- a/BasicFormat/Delivery-Receipt.xlsx
+++ b/BasicFormat/Delivery-Receipt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\BasicFormat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE42A36-CF3E-43F4-AB97-84C6E6DFB461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524A28F2-C155-44DC-A782-128C241457E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery Receipt" sheetId="1" r:id="rId1"/>
@@ -82,16 +82,16 @@
     <t xml:space="preserve">ITEM NAME </t>
   </si>
   <si>
-    <t>Supply chain</t>
-  </si>
-  <si>
-    <t>Alvin</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
-    <t>BACS EMPLOYEE CARD</t>
+    <t>MOHAMMAD EL ASHAR</t>
+  </si>
+  <si>
+    <t>Logistics Manager</t>
+  </si>
+  <si>
+    <t>Mohammad Shariq(#4797) Laptop with Charger</t>
   </si>
 </sst>
 </file>
@@ -427,7 +427,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>48711</xdr:colOff>
+      <xdr:colOff>54426</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>645511</xdr:rowOff>
     </xdr:to>
@@ -782,7 +782,7 @@
       <c r="B2" s="23"/>
       <c r="C2" s="17">
         <f ca="1">TODAY()</f>
-        <v>45895</v>
+        <v>46076</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="20"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="13">
-        <v>1861</v>
+        <v>3582</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="20"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="20"/>
@@ -853,12 +853,12 @@
         <v>15</v>
       </c>
       <c r="C9" s="9">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="6">
         <f>C9</f>
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1154,13 +1154,13 @@
         <v>27</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="19"/>
       <c r="E34" s="6">
         <f>SUM(E9:E33)</f>
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
